--- a/SPRITES16X16.xlsx
+++ b/SPRITES16X16.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chris\Documents\GitHub\X16-DK-Run\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{636BD0E8-2120-44DE-A287-A75195C83618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{484FE2A5-F715-4737-BB1A-8C644B288787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{398B54D3-B140-4EE8-8868-62DB80319196}"/>
   </bookViews>
@@ -35,7 +35,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="1">
+  <si>
+    <t>DATA</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -258,7 +262,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -266,178 +270,16 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -452,13 +294,6 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -491,6 +326,12 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -820,14 +661,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2204B582-9279-4E20-B894-CF51252B59CA}">
-  <dimension ref="A1:AG21"/>
+  <dimension ref="A1:AK21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="17" width="2" customWidth="1"/>
+    <col min="37" max="37" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:37" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1">
         <v>1</v>
       </c>
@@ -877,443 +719,2140 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:37" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="3"/>
+      <c r="B2" s="2">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4">
+        <v>2</v>
+      </c>
+      <c r="H2" s="4">
+        <v>2</v>
+      </c>
+      <c r="I2" s="4">
+        <v>2</v>
+      </c>
+      <c r="J2" s="4">
+        <v>2</v>
+      </c>
+      <c r="K2" s="4">
+        <v>2</v>
+      </c>
+      <c r="L2" s="2">
+        <v>0</v>
+      </c>
+      <c r="M2" s="2">
+        <v>0</v>
+      </c>
+      <c r="N2" s="2">
+        <v>0</v>
+      </c>
+      <c r="O2" s="2">
+        <v>0</v>
+      </c>
+      <c r="P2" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>0</v>
+      </c>
+      <c r="S2" s="18">
+        <v>6210</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U2" s="1" t="str">
+        <f>","&amp;B2</f>
+        <v>,0</v>
+      </c>
+      <c r="V2" s="1" t="str">
+        <f t="shared" ref="V2:AJ2" si="0">","&amp;C2</f>
+        <v>,0</v>
+      </c>
+      <c r="W2" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>,0</v>
+      </c>
+      <c r="X2" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>,0</v>
+      </c>
+      <c r="Y2" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>,0</v>
+      </c>
+      <c r="Z2" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>,2</v>
+      </c>
+      <c r="AA2" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>,2</v>
+      </c>
+      <c r="AB2" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>,2</v>
+      </c>
+      <c r="AC2" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>,2</v>
+      </c>
+      <c r="AD2" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>,2</v>
+      </c>
+      <c r="AE2" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>,0</v>
+      </c>
+      <c r="AF2" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>,0</v>
+      </c>
+      <c r="AG2" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>,0</v>
+      </c>
+      <c r="AH2" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>,0</v>
+      </c>
+      <c r="AI2" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>,0</v>
+      </c>
+      <c r="AJ2" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>,0</v>
+      </c>
+      <c r="AK2" s="19" t="str">
+        <f>S2&amp;" "&amp;T2&amp;U2&amp;V2&amp;W2&amp;X2&amp;Y2&amp;Z2&amp;AA2&amp;AB2&amp;AC2&amp;AD2&amp;AE2&amp;AF2&amp;AG2&amp;AH2&amp;AI2&amp;AJ2</f>
+        <v>6210 DATA,0,0,0,0,0,2,2,2,2,2,0,0,0,0,0,0</v>
+      </c>
     </row>
-    <row r="3" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:37" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="6"/>
+      <c r="B3" s="2">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4">
+        <v>2</v>
+      </c>
+      <c r="G3" s="4">
+        <v>2</v>
+      </c>
+      <c r="H3" s="4">
+        <v>2</v>
+      </c>
+      <c r="I3" s="4">
+        <v>2</v>
+      </c>
+      <c r="J3" s="4">
+        <v>2</v>
+      </c>
+      <c r="K3" s="4">
+        <v>2</v>
+      </c>
+      <c r="L3" s="4">
+        <v>2</v>
+      </c>
+      <c r="M3" s="4">
+        <v>2</v>
+      </c>
+      <c r="N3" s="4">
+        <v>2</v>
+      </c>
+      <c r="O3" s="2">
+        <v>0</v>
+      </c>
+      <c r="P3" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>0</v>
+      </c>
+      <c r="S3" s="18">
+        <v>6220</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U3" s="1" t="str">
+        <f t="shared" ref="U3:U17" si="1">","&amp;B3</f>
+        <v>,0</v>
+      </c>
+      <c r="V3" s="1" t="str">
+        <f t="shared" ref="V3:V17" si="2">","&amp;C3</f>
+        <v>,0</v>
+      </c>
+      <c r="W3" s="1" t="str">
+        <f t="shared" ref="W3:W17" si="3">","&amp;D3</f>
+        <v>,0</v>
+      </c>
+      <c r="X3" s="1" t="str">
+        <f t="shared" ref="X3:X17" si="4">","&amp;E3</f>
+        <v>,0</v>
+      </c>
+      <c r="Y3" s="1" t="str">
+        <f t="shared" ref="Y3:Y17" si="5">","&amp;F3</f>
+        <v>,2</v>
+      </c>
+      <c r="Z3" s="1" t="str">
+        <f t="shared" ref="Z3:Z17" si="6">","&amp;G3</f>
+        <v>,2</v>
+      </c>
+      <c r="AA3" s="1" t="str">
+        <f t="shared" ref="AA3:AA17" si="7">","&amp;H3</f>
+        <v>,2</v>
+      </c>
+      <c r="AB3" s="1" t="str">
+        <f t="shared" ref="AB3:AB17" si="8">","&amp;I3</f>
+        <v>,2</v>
+      </c>
+      <c r="AC3" s="1" t="str">
+        <f t="shared" ref="AC3:AC17" si="9">","&amp;J3</f>
+        <v>,2</v>
+      </c>
+      <c r="AD3" s="1" t="str">
+        <f t="shared" ref="AD3:AD17" si="10">","&amp;K3</f>
+        <v>,2</v>
+      </c>
+      <c r="AE3" s="1" t="str">
+        <f t="shared" ref="AE3:AE17" si="11">","&amp;L3</f>
+        <v>,2</v>
+      </c>
+      <c r="AF3" s="1" t="str">
+        <f t="shared" ref="AF3:AF17" si="12">","&amp;M3</f>
+        <v>,2</v>
+      </c>
+      <c r="AG3" s="1" t="str">
+        <f t="shared" ref="AG3:AG17" si="13">","&amp;N3</f>
+        <v>,2</v>
+      </c>
+      <c r="AH3" s="1" t="str">
+        <f t="shared" ref="AH3:AH17" si="14">","&amp;O3</f>
+        <v>,0</v>
+      </c>
+      <c r="AI3" s="1" t="str">
+        <f t="shared" ref="AI3:AI17" si="15">","&amp;P3</f>
+        <v>,0</v>
+      </c>
+      <c r="AJ3" s="1" t="str">
+        <f t="shared" ref="AJ3:AJ17" si="16">","&amp;Q3</f>
+        <v>,0</v>
+      </c>
+      <c r="AK3" s="19" t="str">
+        <f t="shared" ref="AK3:AK17" si="17">S3&amp;" "&amp;T3&amp;U3&amp;V3&amp;W3&amp;X3&amp;Y3&amp;Z3&amp;AA3&amp;AB3&amp;AC3&amp;AD3&amp;AE3&amp;AF3&amp;AG3&amp;AH3&amp;AI3&amp;AJ3</f>
+        <v>6220 DATA,0,0,0,0,2,2,2,2,2,2,2,2,2,0,0,0</v>
+      </c>
     </row>
-    <row r="4" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:37" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="6"/>
+      <c r="B4" s="2">
+        <v>0</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+      <c r="F4" s="8">
+        <v>6</v>
+      </c>
+      <c r="G4" s="8">
+        <v>6</v>
+      </c>
+      <c r="H4" s="8">
+        <v>6</v>
+      </c>
+      <c r="I4" s="10">
+        <v>8</v>
+      </c>
+      <c r="J4" s="10">
+        <v>8</v>
+      </c>
+      <c r="K4" s="8">
+        <v>6</v>
+      </c>
+      <c r="L4" s="10">
+        <v>8</v>
+      </c>
+      <c r="M4" s="2">
+        <v>0</v>
+      </c>
+      <c r="N4" s="2">
+        <v>0</v>
+      </c>
+      <c r="O4" s="2">
+        <v>0</v>
+      </c>
+      <c r="P4" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>0</v>
+      </c>
+      <c r="S4" s="18">
+        <v>6230</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U4" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>,0</v>
+      </c>
+      <c r="V4" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>,0</v>
+      </c>
+      <c r="W4" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>,0</v>
+      </c>
+      <c r="X4" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>,0</v>
+      </c>
+      <c r="Y4" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>,6</v>
+      </c>
+      <c r="Z4" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>,6</v>
+      </c>
+      <c r="AA4" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>,6</v>
+      </c>
+      <c r="AB4" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v>,8</v>
+      </c>
+      <c r="AC4" s="1" t="str">
+        <f t="shared" si="9"/>
+        <v>,8</v>
+      </c>
+      <c r="AD4" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>,6</v>
+      </c>
+      <c r="AE4" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>,8</v>
+      </c>
+      <c r="AF4" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>,0</v>
+      </c>
+      <c r="AG4" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>,0</v>
+      </c>
+      <c r="AH4" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>,0</v>
+      </c>
+      <c r="AI4" s="1" t="str">
+        <f t="shared" si="15"/>
+        <v>,0</v>
+      </c>
+      <c r="AJ4" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>,0</v>
+      </c>
+      <c r="AK4" s="19" t="str">
+        <f t="shared" si="17"/>
+        <v>6230 DATA,0,0,0,0,6,6,6,8,8,6,8,0,0,0,0,0</v>
+      </c>
     </row>
-    <row r="5" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:37" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="17"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="6"/>
+      <c r="B5" s="2">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" s="8">
+        <v>6</v>
+      </c>
+      <c r="F5" s="10">
+        <v>8</v>
+      </c>
+      <c r="G5" s="8">
+        <v>6</v>
+      </c>
+      <c r="H5" s="10">
+        <v>8</v>
+      </c>
+      <c r="I5" s="10">
+        <v>8</v>
+      </c>
+      <c r="J5" s="10">
+        <v>8</v>
+      </c>
+      <c r="K5" s="8">
+        <v>6</v>
+      </c>
+      <c r="L5" s="10">
+        <v>8</v>
+      </c>
+      <c r="M5" s="10">
+        <v>8</v>
+      </c>
+      <c r="N5" s="10">
+        <v>8</v>
+      </c>
+      <c r="O5" s="2">
+        <v>0</v>
+      </c>
+      <c r="P5" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>0</v>
+      </c>
+      <c r="S5" s="18">
+        <v>6240</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U5" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>,0</v>
+      </c>
+      <c r="V5" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>,0</v>
+      </c>
+      <c r="W5" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>,0</v>
+      </c>
+      <c r="X5" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>,6</v>
+      </c>
+      <c r="Y5" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>,8</v>
+      </c>
+      <c r="Z5" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>,6</v>
+      </c>
+      <c r="AA5" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>,8</v>
+      </c>
+      <c r="AB5" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v>,8</v>
+      </c>
+      <c r="AC5" s="1" t="str">
+        <f t="shared" si="9"/>
+        <v>,8</v>
+      </c>
+      <c r="AD5" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>,6</v>
+      </c>
+      <c r="AE5" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>,8</v>
+      </c>
+      <c r="AF5" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>,8</v>
+      </c>
+      <c r="AG5" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>,8</v>
+      </c>
+      <c r="AH5" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>,0</v>
+      </c>
+      <c r="AI5" s="1" t="str">
+        <f t="shared" si="15"/>
+        <v>,0</v>
+      </c>
+      <c r="AJ5" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>,0</v>
+      </c>
+      <c r="AK5" s="19" t="str">
+        <f t="shared" si="17"/>
+        <v>6240 DATA,0,0,0,6,8,6,8,8,8,6,8,8,8,0,0,0</v>
+      </c>
     </row>
-    <row r="6" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:37" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="6"/>
+      <c r="B6" s="2">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" s="8">
+        <v>6</v>
+      </c>
+      <c r="F6" s="10">
+        <v>8</v>
+      </c>
+      <c r="G6" s="8">
+        <v>6</v>
+      </c>
+      <c r="H6" s="8">
+        <v>6</v>
+      </c>
+      <c r="I6" s="10">
+        <v>8</v>
+      </c>
+      <c r="J6" s="10">
+        <v>8</v>
+      </c>
+      <c r="K6" s="10">
+        <v>8</v>
+      </c>
+      <c r="L6" s="8">
+        <v>6</v>
+      </c>
+      <c r="M6" s="10">
+        <v>8</v>
+      </c>
+      <c r="N6" s="10">
+        <v>8</v>
+      </c>
+      <c r="O6" s="10">
+        <v>8</v>
+      </c>
+      <c r="P6" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>0</v>
+      </c>
+      <c r="S6" s="18">
+        <v>6250</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U6" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>,0</v>
+      </c>
+      <c r="V6" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>,0</v>
+      </c>
+      <c r="W6" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>,0</v>
+      </c>
+      <c r="X6" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>,6</v>
+      </c>
+      <c r="Y6" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>,8</v>
+      </c>
+      <c r="Z6" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>,6</v>
+      </c>
+      <c r="AA6" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>,6</v>
+      </c>
+      <c r="AB6" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v>,8</v>
+      </c>
+      <c r="AC6" s="1" t="str">
+        <f t="shared" si="9"/>
+        <v>,8</v>
+      </c>
+      <c r="AD6" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>,8</v>
+      </c>
+      <c r="AE6" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>,6</v>
+      </c>
+      <c r="AF6" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>,8</v>
+      </c>
+      <c r="AG6" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>,8</v>
+      </c>
+      <c r="AH6" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>,8</v>
+      </c>
+      <c r="AI6" s="1" t="str">
+        <f t="shared" si="15"/>
+        <v>,0</v>
+      </c>
+      <c r="AJ6" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>,0</v>
+      </c>
+      <c r="AK6" s="19" t="str">
+        <f t="shared" si="17"/>
+        <v>6250 DATA,0,0,0,6,8,6,6,8,8,8,6,8,8,8,0,0</v>
+      </c>
     </row>
-    <row r="7" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:37" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="6"/>
+      <c r="B7" s="2">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
+      <c r="F7" s="8">
+        <v>6</v>
+      </c>
+      <c r="G7" s="10">
+        <v>8</v>
+      </c>
+      <c r="H7" s="10">
+        <v>8</v>
+      </c>
+      <c r="I7" s="10">
+        <v>8</v>
+      </c>
+      <c r="J7" s="10">
+        <v>8</v>
+      </c>
+      <c r="K7" s="8">
+        <v>6</v>
+      </c>
+      <c r="L7" s="8">
+        <v>6</v>
+      </c>
+      <c r="M7" s="8">
+        <v>6</v>
+      </c>
+      <c r="N7" s="8">
+        <v>6</v>
+      </c>
+      <c r="O7" s="2">
+        <v>0</v>
+      </c>
+      <c r="P7" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>0</v>
+      </c>
+      <c r="S7" s="18">
+        <v>6260</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U7" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>,0</v>
+      </c>
+      <c r="V7" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>,0</v>
+      </c>
+      <c r="W7" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>,0</v>
+      </c>
+      <c r="X7" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>,0</v>
+      </c>
+      <c r="Y7" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>,6</v>
+      </c>
+      <c r="Z7" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>,8</v>
+      </c>
+      <c r="AA7" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>,8</v>
+      </c>
+      <c r="AB7" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v>,8</v>
+      </c>
+      <c r="AC7" s="1" t="str">
+        <f t="shared" si="9"/>
+        <v>,8</v>
+      </c>
+      <c r="AD7" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>,6</v>
+      </c>
+      <c r="AE7" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>,6</v>
+      </c>
+      <c r="AF7" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>,6</v>
+      </c>
+      <c r="AG7" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>,6</v>
+      </c>
+      <c r="AH7" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>,0</v>
+      </c>
+      <c r="AI7" s="1" t="str">
+        <f t="shared" si="15"/>
+        <v>,0</v>
+      </c>
+      <c r="AJ7" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>,0</v>
+      </c>
+      <c r="AK7" s="19" t="str">
+        <f t="shared" si="17"/>
+        <v>6260 DATA,0,0,0,0,6,8,8,8,8,6,6,6,6,0,0,0</v>
+      </c>
     </row>
-    <row r="8" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:37" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="6"/>
+      <c r="B8" s="2">
+        <v>0</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
+      <c r="G8" s="10">
+        <v>8</v>
+      </c>
+      <c r="H8" s="10">
+        <v>8</v>
+      </c>
+      <c r="I8" s="10">
+        <v>8</v>
+      </c>
+      <c r="J8" s="10">
+        <v>8</v>
+      </c>
+      <c r="K8" s="10">
+        <v>8</v>
+      </c>
+      <c r="L8" s="10">
+        <v>8</v>
+      </c>
+      <c r="M8" s="2">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2">
+        <v>0</v>
+      </c>
+      <c r="O8" s="2">
+        <v>0</v>
+      </c>
+      <c r="P8" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>0</v>
+      </c>
+      <c r="S8" s="18">
+        <v>6270</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U8" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>,0</v>
+      </c>
+      <c r="V8" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>,0</v>
+      </c>
+      <c r="W8" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>,0</v>
+      </c>
+      <c r="X8" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>,0</v>
+      </c>
+      <c r="Y8" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>,0</v>
+      </c>
+      <c r="Z8" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>,8</v>
+      </c>
+      <c r="AA8" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>,8</v>
+      </c>
+      <c r="AB8" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v>,8</v>
+      </c>
+      <c r="AC8" s="1" t="str">
+        <f t="shared" si="9"/>
+        <v>,8</v>
+      </c>
+      <c r="AD8" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>,8</v>
+      </c>
+      <c r="AE8" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>,8</v>
+      </c>
+      <c r="AF8" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>,0</v>
+      </c>
+      <c r="AG8" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>,0</v>
+      </c>
+      <c r="AH8" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>,0</v>
+      </c>
+      <c r="AI8" s="1" t="str">
+        <f t="shared" si="15"/>
+        <v>,0</v>
+      </c>
+      <c r="AJ8" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>,0</v>
+      </c>
+      <c r="AK8" s="19" t="str">
+        <f t="shared" si="17"/>
+        <v>6270 DATA,0,0,0,0,0,8,8,8,8,8,8,0,0,0,0,0</v>
+      </c>
     </row>
-    <row r="9" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:37" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="19"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="21"/>
-      <c r="J9" s="20"/>
-      <c r="K9" s="20"/>
-      <c r="L9" s="20"/>
-      <c r="M9" s="20"/>
-      <c r="N9" s="20"/>
-      <c r="O9" s="20"/>
-      <c r="P9" s="20"/>
-      <c r="Q9" s="22"/>
+      <c r="B9" s="2">
+        <v>0</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4">
+        <v>2</v>
+      </c>
+      <c r="G9" s="4">
+        <v>2</v>
+      </c>
+      <c r="H9" s="8">
+        <v>6</v>
+      </c>
+      <c r="I9" s="4">
+        <v>2</v>
+      </c>
+      <c r="J9" s="4">
+        <v>2</v>
+      </c>
+      <c r="K9" s="8">
+        <v>6</v>
+      </c>
+      <c r="L9" s="4">
+        <v>2</v>
+      </c>
+      <c r="M9" s="4">
+        <v>2</v>
+      </c>
+      <c r="N9" s="2">
+        <v>0</v>
+      </c>
+      <c r="O9" s="2">
+        <v>0</v>
+      </c>
+      <c r="P9" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>0</v>
+      </c>
+      <c r="S9" s="18">
+        <v>6280</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U9" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>,0</v>
+      </c>
+      <c r="V9" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>,0</v>
+      </c>
+      <c r="W9" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>,0</v>
+      </c>
+      <c r="X9" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>,0</v>
+      </c>
+      <c r="Y9" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>,2</v>
+      </c>
+      <c r="Z9" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>,2</v>
+      </c>
+      <c r="AA9" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>,6</v>
+      </c>
+      <c r="AB9" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v>,2</v>
+      </c>
+      <c r="AC9" s="1" t="str">
+        <f t="shared" si="9"/>
+        <v>,2</v>
+      </c>
+      <c r="AD9" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>,6</v>
+      </c>
+      <c r="AE9" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>,2</v>
+      </c>
+      <c r="AF9" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>,2</v>
+      </c>
+      <c r="AG9" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>,0</v>
+      </c>
+      <c r="AH9" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>,0</v>
+      </c>
+      <c r="AI9" s="1" t="str">
+        <f t="shared" si="15"/>
+        <v>,0</v>
+      </c>
+      <c r="AJ9" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>,0</v>
+      </c>
+      <c r="AK9" s="19" t="str">
+        <f t="shared" si="17"/>
+        <v>6280 DATA,0,0,0,0,2,2,6,2,2,6,2,2,0,0,0,0</v>
+      </c>
     </row>
-    <row r="10" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:37" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="6"/>
+      <c r="B10" s="2">
+        <v>0</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0</v>
+      </c>
+      <c r="E10" s="4">
+        <v>2</v>
+      </c>
+      <c r="F10" s="4">
+        <v>2</v>
+      </c>
+      <c r="G10" s="4">
+        <v>2</v>
+      </c>
+      <c r="H10" s="8">
+        <v>6</v>
+      </c>
+      <c r="I10" s="4">
+        <v>2</v>
+      </c>
+      <c r="J10" s="4">
+        <v>2</v>
+      </c>
+      <c r="K10" s="8">
+        <v>6</v>
+      </c>
+      <c r="L10" s="4">
+        <v>2</v>
+      </c>
+      <c r="M10" s="4">
+        <v>2</v>
+      </c>
+      <c r="N10" s="4">
+        <v>2</v>
+      </c>
+      <c r="O10" s="2">
+        <v>0</v>
+      </c>
+      <c r="P10" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>0</v>
+      </c>
+      <c r="S10" s="18">
+        <v>6290</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U10" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>,0</v>
+      </c>
+      <c r="V10" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>,0</v>
+      </c>
+      <c r="W10" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>,0</v>
+      </c>
+      <c r="X10" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>,2</v>
+      </c>
+      <c r="Y10" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>,2</v>
+      </c>
+      <c r="Z10" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>,2</v>
+      </c>
+      <c r="AA10" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>,6</v>
+      </c>
+      <c r="AB10" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v>,2</v>
+      </c>
+      <c r="AC10" s="1" t="str">
+        <f t="shared" si="9"/>
+        <v>,2</v>
+      </c>
+      <c r="AD10" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>,6</v>
+      </c>
+      <c r="AE10" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>,2</v>
+      </c>
+      <c r="AF10" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>,2</v>
+      </c>
+      <c r="AG10" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>,2</v>
+      </c>
+      <c r="AH10" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>,0</v>
+      </c>
+      <c r="AI10" s="1" t="str">
+        <f t="shared" si="15"/>
+        <v>,0</v>
+      </c>
+      <c r="AJ10" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>,0</v>
+      </c>
+      <c r="AK10" s="19" t="str">
+        <f t="shared" si="17"/>
+        <v>6290 DATA,0,0,0,2,2,2,6,2,2,6,2,2,2,0,0,0</v>
+      </c>
     </row>
-    <row r="11" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:37" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="17"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="6"/>
+      <c r="B11" s="2">
+        <v>0</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0</v>
+      </c>
+      <c r="D11" s="4">
+        <v>2</v>
+      </c>
+      <c r="E11" s="4">
+        <v>2</v>
+      </c>
+      <c r="F11" s="4">
+        <v>2</v>
+      </c>
+      <c r="G11" s="4">
+        <v>2</v>
+      </c>
+      <c r="H11" s="8">
+        <v>6</v>
+      </c>
+      <c r="I11" s="8">
+        <v>6</v>
+      </c>
+      <c r="J11" s="8">
+        <v>6</v>
+      </c>
+      <c r="K11" s="8">
+        <v>6</v>
+      </c>
+      <c r="L11" s="4">
+        <v>2</v>
+      </c>
+      <c r="M11" s="4">
+        <v>2</v>
+      </c>
+      <c r="N11" s="4">
+        <v>2</v>
+      </c>
+      <c r="O11" s="4">
+        <v>2</v>
+      </c>
+      <c r="P11" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>0</v>
+      </c>
+      <c r="S11" s="18">
+        <v>6300</v>
+      </c>
+      <c r="T11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U11" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>,0</v>
+      </c>
+      <c r="V11" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>,0</v>
+      </c>
+      <c r="W11" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>,2</v>
+      </c>
+      <c r="X11" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>,2</v>
+      </c>
+      <c r="Y11" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>,2</v>
+      </c>
+      <c r="Z11" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>,2</v>
+      </c>
+      <c r="AA11" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>,6</v>
+      </c>
+      <c r="AB11" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v>,6</v>
+      </c>
+      <c r="AC11" s="1" t="str">
+        <f t="shared" si="9"/>
+        <v>,6</v>
+      </c>
+      <c r="AD11" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>,6</v>
+      </c>
+      <c r="AE11" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>,2</v>
+      </c>
+      <c r="AF11" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>,2</v>
+      </c>
+      <c r="AG11" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>,2</v>
+      </c>
+      <c r="AH11" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>,2</v>
+      </c>
+      <c r="AI11" s="1" t="str">
+        <f t="shared" si="15"/>
+        <v>,0</v>
+      </c>
+      <c r="AJ11" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>,0</v>
+      </c>
+      <c r="AK11" s="19" t="str">
+        <f t="shared" si="17"/>
+        <v>6300 DATA,0,0,2,2,2,2,6,6,6,6,2,2,2,2,0,0</v>
+      </c>
     </row>
-    <row r="12" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:37" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-      <c r="P12" s="5"/>
-      <c r="Q12" s="6"/>
+      <c r="B12" s="2">
+        <v>0</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0</v>
+      </c>
+      <c r="D12" s="10">
+        <v>8</v>
+      </c>
+      <c r="E12" s="10">
+        <v>8</v>
+      </c>
+      <c r="F12" s="4">
+        <v>2</v>
+      </c>
+      <c r="G12" s="8">
+        <v>6</v>
+      </c>
+      <c r="H12" s="9">
+        <v>7</v>
+      </c>
+      <c r="I12" s="8">
+        <v>6</v>
+      </c>
+      <c r="J12" s="8">
+        <v>6</v>
+      </c>
+      <c r="K12" s="9">
+        <v>7</v>
+      </c>
+      <c r="L12" s="8">
+        <v>6</v>
+      </c>
+      <c r="M12" s="4">
+        <v>2</v>
+      </c>
+      <c r="N12" s="10">
+        <v>8</v>
+      </c>
+      <c r="O12" s="10">
+        <v>8</v>
+      </c>
+      <c r="P12" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>0</v>
+      </c>
+      <c r="S12" s="18">
+        <v>6310</v>
+      </c>
+      <c r="T12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U12" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>,0</v>
+      </c>
+      <c r="V12" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>,0</v>
+      </c>
+      <c r="W12" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>,8</v>
+      </c>
+      <c r="X12" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>,8</v>
+      </c>
+      <c r="Y12" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>,2</v>
+      </c>
+      <c r="Z12" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>,6</v>
+      </c>
+      <c r="AA12" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>,7</v>
+      </c>
+      <c r="AB12" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v>,6</v>
+      </c>
+      <c r="AC12" s="1" t="str">
+        <f t="shared" si="9"/>
+        <v>,6</v>
+      </c>
+      <c r="AD12" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>,7</v>
+      </c>
+      <c r="AE12" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>,6</v>
+      </c>
+      <c r="AF12" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>,2</v>
+      </c>
+      <c r="AG12" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>,8</v>
+      </c>
+      <c r="AH12" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>,8</v>
+      </c>
+      <c r="AI12" s="1" t="str">
+        <f t="shared" si="15"/>
+        <v>,0</v>
+      </c>
+      <c r="AJ12" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>,0</v>
+      </c>
+      <c r="AK12" s="19" t="str">
+        <f t="shared" si="17"/>
+        <v>6310 DATA,0,0,8,8,2,6,7,6,6,7,6,2,8,8,0,0</v>
+      </c>
     </row>
-    <row r="13" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:37" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="6"/>
+      <c r="B13" s="2">
+        <v>0</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0</v>
+      </c>
+      <c r="D13" s="10">
+        <v>8</v>
+      </c>
+      <c r="E13" s="10">
+        <v>8</v>
+      </c>
+      <c r="F13" s="10">
+        <v>8</v>
+      </c>
+      <c r="G13" s="8">
+        <v>6</v>
+      </c>
+      <c r="H13" s="8">
+        <v>6</v>
+      </c>
+      <c r="I13" s="8">
+        <v>6</v>
+      </c>
+      <c r="J13" s="8">
+        <v>6</v>
+      </c>
+      <c r="K13" s="8">
+        <v>6</v>
+      </c>
+      <c r="L13" s="8">
+        <v>6</v>
+      </c>
+      <c r="M13" s="10">
+        <v>8</v>
+      </c>
+      <c r="N13" s="10">
+        <v>8</v>
+      </c>
+      <c r="O13" s="10">
+        <v>8</v>
+      </c>
+      <c r="P13" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>0</v>
+      </c>
+      <c r="S13" s="18">
+        <v>6320</v>
+      </c>
+      <c r="T13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U13" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>,0</v>
+      </c>
+      <c r="V13" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>,0</v>
+      </c>
+      <c r="W13" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>,8</v>
+      </c>
+      <c r="X13" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>,8</v>
+      </c>
+      <c r="Y13" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>,8</v>
+      </c>
+      <c r="Z13" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>,6</v>
+      </c>
+      <c r="AA13" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>,6</v>
+      </c>
+      <c r="AB13" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v>,6</v>
+      </c>
+      <c r="AC13" s="1" t="str">
+        <f t="shared" si="9"/>
+        <v>,6</v>
+      </c>
+      <c r="AD13" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>,6</v>
+      </c>
+      <c r="AE13" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>,6</v>
+      </c>
+      <c r="AF13" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>,8</v>
+      </c>
+      <c r="AG13" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>,8</v>
+      </c>
+      <c r="AH13" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>,8</v>
+      </c>
+      <c r="AI13" s="1" t="str">
+        <f t="shared" si="15"/>
+        <v>,0</v>
+      </c>
+      <c r="AJ13" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>,0</v>
+      </c>
+      <c r="AK13" s="19" t="str">
+        <f t="shared" si="17"/>
+        <v>6320 DATA,0,0,8,8,8,6,6,6,6,6,6,8,8,8,0,0</v>
+      </c>
     </row>
-    <row r="14" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:37" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="6"/>
+      <c r="B14" s="2">
+        <v>0</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0</v>
+      </c>
+      <c r="D14" s="10">
+        <v>8</v>
+      </c>
+      <c r="E14" s="10">
+        <v>8</v>
+      </c>
+      <c r="F14" s="8">
+        <v>6</v>
+      </c>
+      <c r="G14" s="8">
+        <v>6</v>
+      </c>
+      <c r="H14" s="8">
+        <v>6</v>
+      </c>
+      <c r="I14" s="8">
+        <v>6</v>
+      </c>
+      <c r="J14" s="8">
+        <v>6</v>
+      </c>
+      <c r="K14" s="8">
+        <v>6</v>
+      </c>
+      <c r="L14" s="8">
+        <v>6</v>
+      </c>
+      <c r="M14" s="8">
+        <v>6</v>
+      </c>
+      <c r="N14" s="10">
+        <v>8</v>
+      </c>
+      <c r="O14" s="10">
+        <v>8</v>
+      </c>
+      <c r="P14" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>0</v>
+      </c>
+      <c r="S14" s="18">
+        <v>6330</v>
+      </c>
+      <c r="T14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U14" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>,0</v>
+      </c>
+      <c r="V14" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>,0</v>
+      </c>
+      <c r="W14" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>,8</v>
+      </c>
+      <c r="X14" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>,8</v>
+      </c>
+      <c r="Y14" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>,6</v>
+      </c>
+      <c r="Z14" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>,6</v>
+      </c>
+      <c r="AA14" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>,6</v>
+      </c>
+      <c r="AB14" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v>,6</v>
+      </c>
+      <c r="AC14" s="1" t="str">
+        <f t="shared" si="9"/>
+        <v>,6</v>
+      </c>
+      <c r="AD14" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>,6</v>
+      </c>
+      <c r="AE14" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>,6</v>
+      </c>
+      <c r="AF14" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>,6</v>
+      </c>
+      <c r="AG14" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>,8</v>
+      </c>
+      <c r="AH14" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>,8</v>
+      </c>
+      <c r="AI14" s="1" t="str">
+        <f t="shared" si="15"/>
+        <v>,0</v>
+      </c>
+      <c r="AJ14" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>,0</v>
+      </c>
+      <c r="AK14" s="19" t="str">
+        <f t="shared" si="17"/>
+        <v>6330 DATA,0,0,8,8,6,6,6,6,6,6,6,6,8,8,0,0</v>
+      </c>
     </row>
-    <row r="15" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:37" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
-      <c r="P15" s="5"/>
-      <c r="Q15" s="6"/>
+      <c r="B15" s="2">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+      <c r="F15" s="8">
+        <v>6</v>
+      </c>
+      <c r="G15" s="8">
+        <v>6</v>
+      </c>
+      <c r="H15" s="8">
+        <v>6</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2">
+        <v>0</v>
+      </c>
+      <c r="K15" s="8">
+        <v>6</v>
+      </c>
+      <c r="L15" s="8">
+        <v>6</v>
+      </c>
+      <c r="M15" s="8">
+        <v>6</v>
+      </c>
+      <c r="N15" s="2">
+        <v>0</v>
+      </c>
+      <c r="O15" s="2">
+        <v>0</v>
+      </c>
+      <c r="P15" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>0</v>
+      </c>
+      <c r="S15" s="18">
+        <v>6340</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U15" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>,0</v>
+      </c>
+      <c r="V15" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>,0</v>
+      </c>
+      <c r="W15" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>,0</v>
+      </c>
+      <c r="X15" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>,0</v>
+      </c>
+      <c r="Y15" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>,6</v>
+      </c>
+      <c r="Z15" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>,6</v>
+      </c>
+      <c r="AA15" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>,6</v>
+      </c>
+      <c r="AB15" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v>,0</v>
+      </c>
+      <c r="AC15" s="1" t="str">
+        <f t="shared" si="9"/>
+        <v>,0</v>
+      </c>
+      <c r="AD15" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>,6</v>
+      </c>
+      <c r="AE15" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>,6</v>
+      </c>
+      <c r="AF15" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>,6</v>
+      </c>
+      <c r="AG15" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>,0</v>
+      </c>
+      <c r="AH15" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>,0</v>
+      </c>
+      <c r="AI15" s="1" t="str">
+        <f t="shared" si="15"/>
+        <v>,0</v>
+      </c>
+      <c r="AJ15" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>,0</v>
+      </c>
+      <c r="AK15" s="19" t="str">
+        <f t="shared" si="17"/>
+        <v>6340 DATA,0,0,0,0,6,6,6,0,0,6,6,6,0,0,0,0</v>
+      </c>
     </row>
-    <row r="16" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:37" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="17"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="5"/>
-      <c r="M16" s="5"/>
-      <c r="N16" s="5"/>
-      <c r="O16" s="5"/>
-      <c r="P16" s="5"/>
-      <c r="Q16" s="6"/>
+      <c r="B16" s="2">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0</v>
+      </c>
+      <c r="E16" s="4">
+        <v>2</v>
+      </c>
+      <c r="F16" s="4">
+        <v>2</v>
+      </c>
+      <c r="G16" s="4">
+        <v>2</v>
+      </c>
+      <c r="H16" s="2">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2">
+        <v>0</v>
+      </c>
+      <c r="K16" s="2">
+        <v>0</v>
+      </c>
+      <c r="L16" s="4">
+        <v>2</v>
+      </c>
+      <c r="M16" s="4">
+        <v>2</v>
+      </c>
+      <c r="N16" s="4">
+        <v>2</v>
+      </c>
+      <c r="O16" s="4">
+        <v>2</v>
+      </c>
+      <c r="P16" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>0</v>
+      </c>
+      <c r="S16" s="18">
+        <v>6350</v>
+      </c>
+      <c r="T16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U16" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>,0</v>
+      </c>
+      <c r="V16" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>,0</v>
+      </c>
+      <c r="W16" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>,0</v>
+      </c>
+      <c r="X16" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>,2</v>
+      </c>
+      <c r="Y16" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>,2</v>
+      </c>
+      <c r="Z16" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>,2</v>
+      </c>
+      <c r="AA16" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>,0</v>
+      </c>
+      <c r="AB16" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v>,0</v>
+      </c>
+      <c r="AC16" s="1" t="str">
+        <f t="shared" si="9"/>
+        <v>,0</v>
+      </c>
+      <c r="AD16" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>,0</v>
+      </c>
+      <c r="AE16" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>,2</v>
+      </c>
+      <c r="AF16" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>,2</v>
+      </c>
+      <c r="AG16" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>,2</v>
+      </c>
+      <c r="AH16" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>,2</v>
+      </c>
+      <c r="AI16" s="1" t="str">
+        <f t="shared" si="15"/>
+        <v>,0</v>
+      </c>
+      <c r="AJ16" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>,0</v>
+      </c>
+      <c r="AK16" s="19" t="str">
+        <f t="shared" si="17"/>
+        <v>6350 DATA,0,0,0,2,2,2,0,0,0,0,2,2,2,2,0,0</v>
+      </c>
     </row>
-    <row r="17" spans="1:33" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:37" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="8"/>
-      <c r="N17" s="8"/>
-      <c r="O17" s="8"/>
-      <c r="P17" s="8"/>
-      <c r="Q17" s="9"/>
+      <c r="B17" s="2">
+        <v>0</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0</v>
+      </c>
+      <c r="D17" s="4">
+        <v>2</v>
+      </c>
+      <c r="E17" s="4">
+        <v>2</v>
+      </c>
+      <c r="F17" s="4">
+        <v>2</v>
+      </c>
+      <c r="G17" s="4">
+        <v>2</v>
+      </c>
+      <c r="H17" s="2">
+        <v>0</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0</v>
+      </c>
+      <c r="J17" s="2">
+        <v>0</v>
+      </c>
+      <c r="K17" s="2">
+        <v>0</v>
+      </c>
+      <c r="L17" s="4">
+        <v>2</v>
+      </c>
+      <c r="M17" s="4">
+        <v>2</v>
+      </c>
+      <c r="N17" s="4">
+        <v>2</v>
+      </c>
+      <c r="O17" s="4">
+        <v>2</v>
+      </c>
+      <c r="P17" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>0</v>
+      </c>
+      <c r="S17" s="18">
+        <v>6360</v>
+      </c>
+      <c r="T17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U17" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>,0</v>
+      </c>
+      <c r="V17" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>,0</v>
+      </c>
+      <c r="W17" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>,2</v>
+      </c>
+      <c r="X17" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>,2</v>
+      </c>
+      <c r="Y17" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>,2</v>
+      </c>
+      <c r="Z17" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>,2</v>
+      </c>
+      <c r="AA17" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>,0</v>
+      </c>
+      <c r="AB17" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v>,0</v>
+      </c>
+      <c r="AC17" s="1" t="str">
+        <f t="shared" si="9"/>
+        <v>,0</v>
+      </c>
+      <c r="AD17" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>,0</v>
+      </c>
+      <c r="AE17" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>,2</v>
+      </c>
+      <c r="AF17" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>,2</v>
+      </c>
+      <c r="AG17" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>,2</v>
+      </c>
+      <c r="AH17" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>,2</v>
+      </c>
+      <c r="AI17" s="1" t="str">
+        <f t="shared" si="15"/>
+        <v>,0</v>
+      </c>
+      <c r="AJ17" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>,0</v>
+      </c>
+      <c r="AK17" s="19" t="str">
+        <f t="shared" si="17"/>
+        <v>6360 DATA,0,0,2,2,2,2,0,0,0,0,2,2,2,2,0,0</v>
+      </c>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="R20" s="10">
-        <v>0</v>
-      </c>
-      <c r="S20" s="10">
+    <row r="20" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="R20" s="1">
+        <v>0</v>
+      </c>
+      <c r="S20" s="1">
         <v>1</v>
       </c>
-      <c r="T20" s="10">
-        <v>2</v>
-      </c>
-      <c r="U20" s="10">
+      <c r="T20" s="1">
+        <v>2</v>
+      </c>
+      <c r="U20" s="1">
         <v>3</v>
       </c>
-      <c r="V20" s="10">
+      <c r="V20" s="1">
         <v>4</v>
       </c>
-      <c r="W20" s="10">
+      <c r="W20" s="1">
         <v>5</v>
       </c>
-      <c r="X20" s="10">
-        <v>6</v>
-      </c>
-      <c r="Y20" s="10">
+      <c r="X20" s="1">
+        <v>6</v>
+      </c>
+      <c r="Y20" s="1">
         <v>7</v>
       </c>
-      <c r="Z20" s="10">
-        <v>8</v>
-      </c>
-      <c r="AA20" s="10">
+      <c r="Z20" s="1">
+        <v>8</v>
+      </c>
+      <c r="AA20" s="1">
         <v>9</v>
       </c>
-      <c r="AB20" s="10">
+      <c r="AB20" s="1">
         <v>10</v>
       </c>
-      <c r="AC20" s="10">
+      <c r="AC20" s="1">
         <v>11</v>
       </c>
-      <c r="AD20" s="10">
+      <c r="AD20" s="1">
         <v>12</v>
       </c>
-      <c r="AE20" s="10">
+      <c r="AE20" s="1">
         <v>13</v>
       </c>
-      <c r="AF20" s="10">
+      <c r="AF20" s="1">
         <v>14</v>
       </c>
-      <c r="AG20" s="10">
+      <c r="AG20" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:33" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="R21" s="11">
-        <v>0</v>
-      </c>
-      <c r="S21" s="12">
+    <row r="21" spans="1:37" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R21" s="2">
+        <v>0</v>
+      </c>
+      <c r="S21" s="3">
         <v>1</v>
       </c>
-      <c r="T21" s="13">
-        <v>2</v>
-      </c>
-      <c r="U21" s="14">
+      <c r="T21" s="4">
+        <v>2</v>
+      </c>
+      <c r="U21" s="5">
         <v>3</v>
       </c>
-      <c r="V21" s="15">
+      <c r="V21" s="6">
         <v>4</v>
       </c>
-      <c r="W21" s="23">
+      <c r="W21" s="7">
         <v>5</v>
       </c>
-      <c r="X21" s="24">
-        <v>6</v>
-      </c>
-      <c r="Y21" s="25">
+      <c r="X21" s="8">
+        <v>6</v>
+      </c>
+      <c r="Y21" s="9">
         <v>7</v>
       </c>
-      <c r="Z21" s="26">
-        <v>8</v>
-      </c>
-      <c r="AA21" s="27">
+      <c r="Z21" s="10">
+        <v>8</v>
+      </c>
+      <c r="AA21" s="11">
         <v>9</v>
       </c>
-      <c r="AB21" s="28">
+      <c r="AB21" s="12">
         <v>10</v>
       </c>
-      <c r="AC21" s="29">
+      <c r="AC21" s="13">
         <v>11</v>
       </c>
-      <c r="AD21" s="30">
+      <c r="AD21" s="14">
         <v>12</v>
       </c>
-      <c r="AE21" s="31">
+      <c r="AE21" s="15">
         <v>13</v>
       </c>
-      <c r="AF21" s="32">
+      <c r="AF21" s="16">
         <v>14</v>
       </c>
-      <c r="AG21" s="33">
+      <c r="AG21" s="17">
         <v>15</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>